--- a/business_forms/030_yacht_preference_sheet_form--business_forms.xlsx
+++ b/business_forms/030_yacht_preference_sheet_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'monohull'}</t>
+          <t>monohull</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Monohull'}</t>
+          <t>Monohull</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'catamaran'}</t>
+          <t>catamaran</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Catamaran'}</t>
+          <t>Catamaran</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'speedboat'}</t>
+          <t>speedboat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Speedboat'}</t>
+          <t>Speedboat</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'mediterranean_sea'}</t>
+          <t>mediterranean_sea</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Mediterranean Sea'}</t>
+          <t>Mediterranean Sea</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'red_sea'}</t>
+          <t>red_sea</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Red Sea'}</t>
+          <t>Red Sea</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'caribbean_sea'}</t>
+          <t>caribbean_sea</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Caribbean Sea'}</t>
+          <t>Caribbean Sea</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'shared'}</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Shared'}</t>
+          <t>Shared</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'vip'}</t>
+          <t>vip</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'VIP'}</t>
+          <t>VIP</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'full_service'}</t>
+          <t>full_service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Full service'}</t>
+          <t>Full service</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'half_service'}</t>
+          <t>half_service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Half service'}</t>
+          <t>Half service</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'self-service'}</t>
+          <t>self-service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Self-service'}</t>
+          <t>Self-service</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'soft_drinks'}</t>
+          <t>soft_drinks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Soft drinks'}</t>
+          <t>Soft drinks</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'wine'}</t>
+          <t>wine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Wine'}</t>
+          <t>Wine</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'champagne'}</t>
+          <t>champagne</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Champagne'}</t>
+          <t>Champagne</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'omnivore'}</t>
+          <t>omnivore</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Omnivore'}</t>
+          <t>Omnivore</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'permitted'}</t>
+          <t>permitted</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Permitted'}</t>
+          <t>Permitted</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'forbidden'}</t>
+          <t>forbidden</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Forbidden'}</t>
+          <t>Forbidden</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Jazz'}</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'pop'}</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Pop'}</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'classical'}</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Classical'}</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'movies'}</t>
+          <t>movies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Movies'}</t>
+          <t>Movies</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'games'}</t>
+          <t>games</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Games'}</t>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'books'}</t>
+          <t>books</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Books'}</t>
+          <t>Books</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'tender'}</t>
+          <t>tender</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Tender'}</t>
+          <t>Tender</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'docking'}</t>
+          <t>docking</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Docking'}</t>
+          <t>Docking</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'beach'}</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Beach'}</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
